--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487620_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487620_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7263</v>
+        <v>5.9156</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3504</v>
+        <v>4.6487</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3759</v>
+        <v>1.2669</v>
       </c>
       <c r="G2" t="n">
         <v>2.2523</v>
@@ -610,13 +610,13 @@
         <v>2.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2516</v>
+        <v>1.4409</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0955</v>
+        <v>1.3938</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1561</v>
+        <v>0.0471</v>
       </c>
       <c r="V2" t="n">
         <v>0.2821</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8105</v>
+        <v>5.2146</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4315</v>
+        <v>2.7538</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3791</v>
+        <v>2.4609</v>
       </c>
       <c r="G3" t="n">
         <v>2.6358</v>
@@ -688,13 +688,13 @@
         <v>3.2985</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0491</v>
+        <v>0.355</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7874</v>
+        <v>0.535</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2618</v>
+        <v>-0.18</v>
       </c>
       <c r="V3" t="n">
         <v>1.8358</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5846</v>
+        <v>2.0572</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5588</v>
+        <v>0.4402</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0258</v>
+        <v>1.617</v>
       </c>
       <c r="G4" t="n">
         <v>0.6566</v>
@@ -766,13 +766,13 @@
         <v>2.1344</v>
       </c>
       <c r="S4" t="n">
-        <v>1.522</v>
+        <v>0.9946</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6808</v>
+        <v>0.5622</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.4324</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5642</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7257</v>
+        <v>0.8135</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0218</v>
+        <v>0.0824</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7039</v>
+        <v>0.7311</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2626</v>
@@ -844,13 +844,13 @@
         <v>1.1642</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1759</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0606</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1153</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. MAIGA</t>
+          <t>G. DIAZ MONTERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3182</v>
+        <v>0.6434</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4037</v>
+        <v>-0.0713</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.4728</v>
+        <v>-1.3473</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.009900000000000001</v>
+        <v>1.1007</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.4629</v>
+        <v>-2.448</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.5742</v>
+        <v>0.2788</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3872</v>
+        <v>1.6313</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9614</v>
+        <v>-1.3524</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8987</v>
+        <v>-1.6262</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3971</v>
+        <v>-0.5306</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.5015</v>
+        <v>-1.0956</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1344</v>
+        <v>-5.0448</v>
       </c>
       <c r="R6" t="n">
         <v>2.1344</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3344</v>
+        <v>1.1583</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1664</v>
+        <v>0.5139</v>
       </c>
       <c r="U6" t="n">
-        <v>1.168</v>
+        <v>0.6444</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2239</v>
+        <v>3.6716</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2239</v>
+        <v>4.8955</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. DIAZ MONTERO</t>
+          <t>R. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3009</v>
+        <v>0.2423</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0388</v>
+        <v>-1.6552</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2621</v>
+        <v>1.8976</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3473</v>
+        <v>-0.8829</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1007</v>
+        <v>-0.042</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.448</v>
+        <v>-0.8409</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2788</v>
+        <v>0.8596</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6313</v>
+        <v>0.8774</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3524</v>
+        <v>-0.0178</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6262</v>
+        <v>-1.7425</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5306</v>
+        <v>-0.9195</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0956</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="P7" t="n">
+        <v>0.7761</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-2.9105</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-5.0448</v>
-      </c>
       <c r="R7" t="n">
-        <v>2.1344</v>
+        <v>3.6866</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2853</v>
+        <v>0.067</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1683</v>
+        <v>0.1135</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4536</v>
+        <v>-0.0465</v>
       </c>
       <c r="V7" t="n">
-        <v>3.6716</v>
+        <v>0.2821</v>
       </c>
       <c r="W7" t="n">
-        <v>4.8955</v>
+        <v>0.2821</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CAÑAS</t>
+          <t>N. MAIGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7153</v>
+        <v>-0.3664</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.589</v>
+        <v>-1.4158</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1262</v>
+        <v>1.0494</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8053</v>
+        <v>-3.4728</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5678</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2375</v>
+        <v>-3.4629</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6607</v>
+        <v>-1.5742</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.7013</v>
+        <v>0.3872</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0406</v>
+        <v>-1.9614</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1446</v>
+        <v>-1.8987</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1335</v>
+        <v>-0.3971</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2781</v>
+        <v>-1.5015</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7463</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.1344</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7463</v>
+        <v>2.1344</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8497</v>
+        <v>1.8826</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7896</v>
+        <v>1.0688</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0601</v>
+        <v>0.8137</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.506</v>
+        <v>1.2239</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2821</v>
+        <v>1.2239</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. LARDIES GUILLEN</t>
+          <t>D. FERNANDEZ CAÑAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.922</v>
+        <v>-1.1491</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7378</v>
+        <v>-0.9684</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8158</v>
+        <v>-0.1807</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8829</v>
+        <v>-1.8053</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.042</v>
+        <v>-1.5678</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8409</v>
+        <v>-0.2375</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8596</v>
+        <v>-1.6607</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8774</v>
+        <v>-1.7013</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0178</v>
+        <v>0.0406</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7425</v>
+        <v>-0.1446</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9195</v>
+        <v>0.1335</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.2781</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7761</v>
+        <v>1.7463</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.6866</v>
+        <v>1.7463</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0973</v>
+        <v>0.4158</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9691</v>
+        <v>0.4102</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1283</v>
+        <v>0.0056</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2821</v>
+        <v>-1.506</v>
       </c>
       <c r="W9" t="n">
         <v>0.2821</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6293</v>
+        <v>-2.0243</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4812</v>
+        <v>-3.0398</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8519</v>
+        <v>1.0154</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8247</v>
@@ -1234,13 +1234,13 @@
         <v>1.7463</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5536</v>
+        <v>1.1586</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1058</v>
+        <v>0.5473</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4477</v>
+        <v>0.6113</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.618</v>
+        <v>-2.0629</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2982</v>
+        <v>-3.7977</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6803</v>
+        <v>1.7348</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1882</v>
@@ -1312,13 +1312,13 @@
         <v>2.1344</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.594</v>
+        <v>-0.039</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.424</v>
+        <v>0.0765</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.17</v>
+        <v>-0.1155</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.5593</v>
+        <v>-6.5106</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.635400000000001</v>
+        <v>-7.9136</v>
       </c>
       <c r="F12" t="n">
-        <v>1.076</v>
+        <v>1.4031</v>
       </c>
       <c r="G12" t="n">
         <v>-7.7709</v>
@@ -1390,13 +1390,13 @@
         <v>2.1344</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4482</v>
+        <v>0.6006</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2288</v>
+        <v>0.4929</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2194</v>
+        <v>0.1077</v>
       </c>
       <c r="V12" t="n">
         <v>0.6597</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.187799999999998</v>
+        <v>2.701999999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.7361</v>
+        <v>-10.222</v>
       </c>
       <c r="F13" t="n">
-        <v>12.9241</v>
+        <v>12.9242</v>
       </c>
       <c r="G13" t="n">
         <v>-15.01</v>
@@ -1441,7 +1441,7 @@
         <v>-19.4919</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.6764</v>
+        <v>-3.676399999999999</v>
       </c>
       <c r="K13" t="n">
         <v>8.947299999999998</v>
@@ -1456,7 +1456,7 @@
         <v>-4.4656</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.868300000000001</v>
+        <v>-6.8683</v>
       </c>
       <c r="P13" t="n">
         <v>3.8807</v>
@@ -1468,13 +1468,13 @@
         <v>25.2244</v>
       </c>
       <c r="S13" t="n">
-        <v>6.4321</v>
+        <v>7.946400000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>4.1999</v>
+        <v>5.7141</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2319</v>
+        <v>2.2322</v>
       </c>
       <c r="V13" t="n">
         <v>5.885000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5127</v>
+        <v>2.9404</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3296</v>
+        <v>4.73</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8169</v>
+        <v>-1.7897</v>
       </c>
       <c r="G14" t="n">
         <v>6.4132</v>
@@ -1546,13 +1546,13 @@
         <v>2.3284</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5886</v>
+        <v>-0.1609</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4722</v>
+        <v>-0.0718</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1164</v>
+        <v>-0.0891</v>
       </c>
       <c r="V14" t="n">
         <v>-2.7298</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. SANTAMARIA LEON</t>
+          <t>L. BERMEJO ALCALDE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8056</v>
+        <v>2.0202</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7306</v>
+        <v>-0.043</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5362</v>
+        <v>2.0632</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0239</v>
+        <v>1.537</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7415</v>
+        <v>-0.4416</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2824</v>
+        <v>1.9786</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1358</v>
+        <v>0.7155</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7219</v>
+        <v>0.0659</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5861</v>
+        <v>0.6495</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8881</v>
+        <v>0.8216</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9804</v>
+        <v>-0.5075</v>
       </c>
       <c r="O15" t="n">
-        <v>1.8685</v>
+        <v>1.3291</v>
       </c>
       <c r="P15" t="n">
-        <v>0.194</v>
+        <v>1.9403</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1344</v>
+        <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4123</v>
+        <v>-0.7974</v>
       </c>
       <c r="T15" t="n">
-        <v>0.074</v>
+        <v>-0.3808</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4863</v>
+        <v>-0.4166</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.3776</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. BERMEJO ALCALDE</t>
+          <t>F. SANTAMARIA LEON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5503</v>
+        <v>1.7934</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2431</v>
+        <v>-0.9308</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7934</v>
+        <v>2.7241</v>
       </c>
       <c r="G16" t="n">
-        <v>1.537</v>
+        <v>2.0239</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4416</v>
+        <v>0.7415</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9786</v>
+        <v>1.2824</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7155</v>
+        <v>1.1358</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0659</v>
+        <v>1.7219</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6495</v>
+        <v>-0.5861</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8216</v>
+        <v>0.8881</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5075</v>
+        <v>-0.9804</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3291</v>
+        <v>1.8685</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9403</v>
+        <v>0.194</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9403</v>
+        <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2674</v>
+        <v>-0.4245</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.581</v>
+        <v>-0.1262</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6864</v>
+        <v>-0.2983</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6597</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3776</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2146</v>
+        <v>1.4844</v>
       </c>
       <c r="E17" t="n">
         <v>-1.8925</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1071</v>
+        <v>3.3769</v>
       </c>
       <c r="G17" t="n">
         <v>1.6576</v>
@@ -1780,13 +1780,13 @@
         <v>2.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2191</v>
+        <v>-0.9494</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2894</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9297</v>
+        <v>-0.66</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. TOLOSA OROPESA</t>
+          <t>C. BARROS CONDES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0603</v>
+        <v>-0.0302</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2034</v>
+        <v>-2.9933</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2638</v>
+        <v>2.9631</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5527</v>
+        <v>3.0145</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1491</v>
+        <v>0.7695</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7018</v>
+        <v>2.245</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7665</v>
+        <v>1.3714</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7209</v>
+        <v>1.3841</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0456</v>
+        <v>-0.0127</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2138</v>
+        <v>1.6431</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.87</v>
+        <v>-0.6146</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6562</v>
+        <v>2.2578</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1642</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1045</v>
+        <v>-5.0448</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9403</v>
+        <v>3.2985</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6718</v>
+        <v>-1.5806</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1346</v>
+        <v>-0.8258</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5373</v>
+        <v>-0.7548</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. ALARCON ORTIZ</t>
+          <t>J. SAEZ BENITO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2421</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5603</v>
+        <v>-0.8784999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8024</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.349</v>
+        <v>0.1318</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.4568</v>
+        <v>-1.4698</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1078</v>
+        <v>1.6016</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1445</v>
+        <v>-1.2523</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5684</v>
+        <v>-1.2523</v>
       </c>
       <c r="L19" t="n">
-        <v>0.713</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4935</v>
+        <v>1.3841</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.8883</v>
+        <v>-0.2175</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3948</v>
+        <v>1.6016</v>
       </c>
       <c r="P19" t="n">
-        <v>1.7463</v>
+        <v>0.5821</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7164</v>
+        <v>0.5821</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9215</v>
+        <v>-0.1489</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.12</v>
+        <v>-0.1904</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8015</v>
+        <v>0.0415</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2821</v>
+        <v>-0.6597</v>
       </c>
       <c r="W19" t="n">
-        <v>1.506</v>
+        <v>0.5642</v>
       </c>
       <c r="X19" t="n">
         <v>-1.2239</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SAEZ BENITO</t>
+          <t>M. ALARCON ORTIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3828</v>
+        <v>-0.2877</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9786</v>
+        <v>0.4602</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5958</v>
+        <v>-0.7479</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1318</v>
+        <v>-1.349</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4698</v>
+        <v>-2.4568</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6016</v>
+        <v>1.1078</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2523</v>
+        <v>0.1445</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2523</v>
+        <v>-0.5684</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.713</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3841</v>
+        <v>-1.4935</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2175</v>
+        <v>-1.8883</v>
       </c>
       <c r="O20" t="n">
-        <v>1.6016</v>
+        <v>0.3948</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5821</v>
+        <v>1.7463</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5821</v>
+        <v>2.7164</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.437</v>
+        <v>-0.9671</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2905</v>
+        <v>-0.2201</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1465</v>
+        <v>-0.7469</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6597</v>
+        <v>0.2821</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5642</v>
+        <v>1.506</v>
       </c>
       <c r="X20" t="n">
         <v>-1.2239</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. BARROS CONDES</t>
+          <t>D. TOLOSA OROPESA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.464</v>
+        <v>-0.6488</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2936</v>
+        <v>-2.5037</v>
       </c>
       <c r="F21" t="n">
-        <v>2.8296</v>
+        <v>1.8549</v>
       </c>
       <c r="G21" t="n">
-        <v>3.0145</v>
+        <v>0.5527</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7695</v>
+        <v>-0.1491</v>
       </c>
       <c r="I21" t="n">
-        <v>2.245</v>
+        <v>0.7018</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3714</v>
+        <v>0.7665</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3841</v>
+        <v>0.7209</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0127</v>
+        <v>0.0456</v>
       </c>
       <c r="M21" t="n">
-        <v>1.6431</v>
+        <v>-0.2138</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6146</v>
+        <v>-0.87</v>
       </c>
       <c r="O21" t="n">
-        <v>2.2578</v>
+        <v>0.6562</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.7463</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.0448</v>
+        <v>-3.1045</v>
       </c>
       <c r="R21" t="n">
-        <v>3.2985</v>
+        <v>1.9403</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.0143</v>
+        <v>-0.0373</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1261</v>
+        <v>-0.1657</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8882</v>
+        <v>0.1285</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7987</v>
+        <v>-1.3715</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1029</v>
+        <v>-1.4032</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3042</v>
+        <v>0.0317</v>
       </c>
       <c r="G22" t="n">
         <v>1.5602</v>
@@ -2170,13 +2170,13 @@
         <v>1.1642</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3993</v>
+        <v>-0.1735</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3768</v>
+        <v>0.0765</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0225</v>
+        <v>-0.2501</v>
       </c>
       <c r="V22" t="n">
         <v>-1.788</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1834</v>
+        <v>-3.1562</v>
       </c>
       <c r="E23" t="n">
         <v>-4.4456</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2621</v>
+        <v>1.2894</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9944</v>
@@ -2248,13 +2248,13 @@
         <v>0.9702</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2488</v>
+        <v>-0.2215</v>
       </c>
       <c r="T23" t="n">
         <v>-0.3634</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1146</v>
+        <v>0.1419</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2605</v>
+        <v>-3.1698</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9237</v>
+        <v>-3.0238</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3368</v>
+        <v>-0.146</v>
       </c>
       <c r="G24" t="n">
         <v>0.4623</v>
@@ -2326,13 +2326,13 @@
         <v>1.3582</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3943</v>
+        <v>-0.3037</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4251</v>
+        <v>0.325</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8194</v>
+        <v>-0.6286</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6119</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.187999999999999</v>
+        <v>-0.5205000000000015</v>
       </c>
       <c r="E25" t="n">
-        <v>-12.9241</v>
+        <v>-12.9242</v>
       </c>
       <c r="F25" t="n">
-        <v>11.7361</v>
+        <v>12.4035</v>
       </c>
       <c r="G25" t="n">
         <v>15.0098</v>
@@ -2404,13 +2404,13 @@
         <v>21.3435</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.4322</v>
+        <v>-5.7648</v>
       </c>
       <c r="T25" t="n">
         <v>-2.2321</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.2</v>
+        <v>-3.5325</v>
       </c>
       <c r="V25" t="n">
         <v>-5.8849</v>
